--- a/inspection_forms/045_workplace_health_and_safety_inspection_form--inspection_forms.xlsx
+++ b/inspection_forms/045_workplace_health_and_safety_inspection_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,133 +520,133 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>workplace_safety_section</t>
+          <t>workplace_safety_practices</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Workplace Safety</t>
+          <t>Workplace Safety Practices</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hazards_section</t>
+          <t>hazard_identification</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hazards</t>
+          <t>Hazard Identification</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hazard_identification</t>
+          <t>hazard_severity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hazard Identification</t>
+          <t>Hazard Severity</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hazard_severity</t>
+          <t>safety_meetings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>Safety Meetings</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>workplace_equipment_section</t>
+          <t>safety_procedures</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Workplace Equipment</t>
+          <t>Safety Procedures</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fire_supervision_section</t>
+          <t>emergency_response</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fire Supervision</t>
+          <t>Emergency Response</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fire_extinguisher</t>
+          <t>fire_safety</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fire Extinguisher</t>
+          <t>Fire Safety</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -692,122 +692,122 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>safety_trainings_section</t>
+          <t>fire_exit_path</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Safety Trainings</t>
+          <t>Fire Exit Path</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>safety_trainings_details</t>
+          <t>emergency_exit_signs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Safety Trainings Details</t>
+          <t>Emergency Exit Signs</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>emergency_exit_path_section</t>
+          <t>emergency_exit_lights</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Emergency Exit Path</t>
+          <t>Emergency Exit Lights</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>emergency_exit_path_condition</t>
+          <t>first_aid_kits</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Emergency Exit Path Condition</t>
+          <t>First Aid Kits</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>emergency_exit_signs_section</t>
+          <t>first_aid_kits_contents</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emergency Exit Sign</t>
+          <t>First Aid Kit Contents</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,41 +819,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>emergency_exit_signs_condition</t>
+          <t>emergency_exit_path</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emergency Exit Sign Condition</t>
+          <t>Emergency Exit Path</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>evacuation_plan_section</t>
+          <t>emergency_exit_sign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Evacuation Plan</t>
+          <t>Emergency Exit Sign</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>evacuation_procedure_section</t>
+          <t>evacuation_procedure</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -876,7 +876,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,18 +888,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>first_aid_kits_section</t>
+          <t>safety_trainings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>First Aid Kits</t>
+          <t>Safety Trainings</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,64 +911,64 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>first_aid_kits_contents</t>
+          <t>safety_trainings_details</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>First Aid Kit Contents</t>
+          <t>Safety Trainings Details</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>emergency_exit_lights_section</t>
+          <t>fire_supervision</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Emergency Exit Lights</t>
+          <t>Fire Supervision</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>emergency_exit_path_condition_section</t>
+          <t>fire_supervision_details</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emergency Exit Path</t>
+          <t>Fire Supervision Details</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -980,18 +980,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>emergency_exit_signs_condition_section</t>
+          <t>fire_supervision_frequency</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Emergency Exit Signs Condition</t>
+          <t>Fire Supervision Frequency</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1003,133 +1003,133 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fire_supervision</t>
+          <t>emergency_exit_path_location</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fire Supervision</t>
+          <t>Emergency Exit Path Location</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fire_supervision_details</t>
+          <t>emergency_exit_path_designated</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fire Supervision Details</t>
+          <t>Emergency Exit Path Designated</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fire_supervision_frequency</t>
+          <t>first_aid_kits_location</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fire Supervision Frequency</t>
+          <t>First Aid Kits Location</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>emergency_exit_path_location</t>
+          <t>first_aid_kits_location_designated</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Emergency Exit Path</t>
+          <t>First Aid Kits Location Designated</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>emergency_exit_path_location_designated</t>
+          <t>fire_extinguisher_service</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Emergency Exit Path</t>
+          <t>Fire Extinguisher Service</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>first_aid_kits_location</t>
+          <t>emergency_exit_path_condition</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>First Aid Kits</t>
+          <t>Emergency Exit Path Condition</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1141,64 +1141,64 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>first_aid_kits_location_designated</t>
+          <t>emergency_exit_signs_condition</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>First Aid Kits</t>
+          <t>Emergency Exit Signs Condition</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>fire_extinguisher_service</t>
+          <t>evacuation_plan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fire Extinguisher</t>
+          <t>Evacuation Plan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>emergency_exit_path_condition_designated</t>
+          <t>fire_supervision_details_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Emergency Exit Path</t>
+          <t>Fire Supervision Details 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1210,41 +1210,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>emergency_exit_lights_service</t>
+          <t>first_aid_kits_service</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Emergency Exit Lights</t>
+          <t>First Aid Kits Service</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>emergency_exit_signs_service</t>
+          <t>emergency_exit_path_condition_designated</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Emergency Exit Signs</t>
+          <t>Emergency Exit Path Condition Designated</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1256,18 +1256,18 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>first_aid_kits_service</t>
+          <t>emergency_exit_lights_service</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>First Aid Kits</t>
+          <t>Emergency Exit Lights Service</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1279,271 +1279,18 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>evacuation_plan_service</t>
+          <t>emergency_exit_signs_service</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Evacuation Plan</t>
+          <t>Emergency Exit Signs Service</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>fire_extinguisher_service</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Fire Extinguisher</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>emergency_exit_path_location_service</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Emergency Exit Path</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>fire_supervision_frequency</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Fire Supervision</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>first_aid_kits_location_service</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>First Aid Kits</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>first_aid_kits_location_designated_service</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>First Aid Kits</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>fire_extinguisher_service_frequency</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Fire Extinguisher</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>emergency_exit_path_condition_service</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Emergency Exit Path</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_location_service</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Emergency Exit Signs</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_condition_service</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Emergency Exit Signs</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>first_aid_kits_service_frequency</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>First Aid Kits</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>emergency_exit_path_designated_service</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Emergency Exit Path</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1305,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1586,1292 +1333,748 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hazards_section_choices</t>
+          <t>hazard_severity_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'electrical_hazards'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Electrical hazards'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hazards_section_choices</t>
+          <t>hazard_severity_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'physical_hazards'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Physical hazards'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hazards_section_choices</t>
+          <t>hazard_severity_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'chemical_hazards'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Chemical hazards'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hazards_section_choices</t>
+          <t>safety_meetings_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'biological_hazards'}</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Biological hazards'}</t>
+          <t>Regularly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hazard_severity_choices</t>
+          <t>safety_meetings_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>not_regularly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Not regularly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hazard_severity_choices</t>
+          <t>fire_safety_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hazard_severity_choices</t>
+          <t>fire_safety_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Not working</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>workplace_equipment_section_choices</t>
+          <t>fire_alarm_system_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'fire_extinguishers'}</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Fire Extinguishers'}</t>
+          <t>Installed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>workplace_equipment_section_choices</t>
+          <t>fire_alarm_system_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'first_aid_kits'}</t>
+          <t>not_installed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'First aid kits'}</t>
+          <t>Not installed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>workplace_equipment_section_choices</t>
+          <t>emergency_exit_signs_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'fire_alarms'}</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Fire alarms'}</t>
+          <t>Visible</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>workplace_equipment_section_choices</t>
+          <t>emergency_exit_signs_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'safety_signs'}</t>
+          <t>not_visible</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Safety signs'}</t>
+          <t>Not visible</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fire_supervision_section_choices</t>
+          <t>emergency_exit_lights_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'regularly_inspected'}</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Regularly inspected'}</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fire_supervision_section_choices</t>
+          <t>emergency_exit_lights_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'not_regularly_inspected'}</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Not regularly inspected'}</t>
+          <t>Not working</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fire_extinguisher_choices</t>
+          <t>first_aid_kits_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'working'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Working'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fire_extinguisher_choices</t>
+          <t>first_aid_kits_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_working'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not working'}</t>
+          <t>Not available</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fire_alarm_system_choices</t>
+          <t>emergency_exit_path_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'installed'}</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Installed'}</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fire_alarm_system_choices</t>
+          <t>emergency_exit_path_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'not_installed'}</t>
+          <t>not_clear</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Not installed'}</t>
+          <t>Not clear</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>safety_trainings_section_choices</t>
+          <t>emergency_exit_sign_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Visible</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>safety_trainings_section_choices</t>
+          <t>emergency_exit_sign_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'not_completed'}</t>
+          <t>not_visible</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Not completed'}</t>
+          <t>Not visible</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>emergency_exit_path_condition_choices</t>
+          <t>safety_trainings_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'clear'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Clear'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>emergency_exit_path_condition_choices</t>
+          <t>safety_trainings_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'not_clear'}</t>
+          <t>not_completed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Not clear'}</t>
+          <t>Not completed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>emergency_exit_signs_section_choices</t>
+          <t>fire_supervision_frequency_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'visible'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Visible'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>emergency_exit_signs_section_choices</t>
+          <t>fire_supervision_frequency_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'not_visible'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Not visible'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>emergency_exit_signs_condition_choices</t>
+          <t>fire_supervision_frequency_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'intact'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Intact'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>emergency_exit_signs_condition_choices</t>
+          <t>emergency_exit_path_designated_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'not_intact'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Not intact'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>first_aid_kits_section_choices</t>
+          <t>emergency_exit_path_designated_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'available'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Available'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>first_aid_kits_section_choices</t>
+          <t>first_aid_kits_location_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'not_available'}</t>
+          <t>designated_area</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Not available'}</t>
+          <t>Designated area</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>emergency_exit_lights_section_choices</t>
+          <t>first_aid_kits_location_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'working'}</t>
+          <t>not_designated_area</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Working'}</t>
+          <t>Not designated area</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>emergency_exit_lights_section_choices</t>
+          <t>first_aid_kits_location_designated_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'not_working'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Not working'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>emergency_exit_path_condition_section_choices</t>
+          <t>first_aid_kits_location_designated_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'clear'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Clear'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>emergency_exit_path_condition_section_choices</t>
+          <t>fire_extinguisher_service_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'not_clear'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Not clear'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>emergency_exit_signs_condition_section_choices</t>
+          <t>fire_extinguisher_service_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'intact'}</t>
+          <t>not_monthly</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Intact'}</t>
+          <t>Not monthly</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>emergency_exit_signs_condition_section_choices</t>
+          <t>emergency_exit_path_condition_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'not_intact'}</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Not intact'}</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>fire_supervision_frequency_choices</t>
+          <t>emergency_exit_path_condition_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>not_clear</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Not clear</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>fire_supervision_frequency_choices</t>
+          <t>emergency_exit_signs_condition_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>intact</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Intact</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fire_supervision_frequency_choices</t>
+          <t>emergency_exit_signs_condition_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>not_intact</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Not intact</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>emergency_exit_path_location_designated_choices</t>
+          <t>first_aid_kits_service_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>emergency_exit_path_location_designated_choices</t>
+          <t>first_aid_kits_service_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>not_monthly</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Not monthly</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>first_aid_kits_location_choices</t>
+          <t>emergency_exit_path_condition_designated_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'designated_area'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Designated area'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>first_aid_kits_location_choices</t>
+          <t>emergency_exit_path_condition_designated_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'not_designated_area'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Not designated area'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>first_aid_kits_location_designated_choices</t>
+          <t>emergency_exit_lights_service_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>first_aid_kits_location_designated_choices</t>
+          <t>emergency_exit_lights_service_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Not working</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>fire_extinguisher_service_choices</t>
+          <t>emergency_exit_signs_service_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Visible</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>fire_extinguisher_service_choices</t>
+          <t>emergency_exit_signs_service_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'not_monthly'}</t>
+          <t>not_visible</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Not monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>emergency_exit_path_condition_designated_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'label':_true}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>emergency_exit_path_condition_designated_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'label':_false}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>emergency_exit_lights_service_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>emergency_exit_lights_service_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'label':_'not_monthly'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'label': 'Not monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_service_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_service_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'label':_'not_monthly'}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'label': 'Not monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>first_aid_kits_service_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>first_aid_kits_service_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'label':_'not_monthly'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'label': 'Not monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>evacuation_plan_service_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>{'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>{'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>evacuation_plan_service_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>{'label':_'not_monthly'}</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>{'label': 'Not monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>fire_extinguisher_service_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>{'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>{'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>fire_extinguisher_service_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>{'label':_'not_monthly'}</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>{'label': 'Not monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>emergency_exit_path_location_service_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>{'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>{'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>emergency_exit_path_location_service_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>{'label':_'not_monthly'}</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>{'label': 'Not monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>fire_supervision_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>{'label':_'daily'}</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>{'label': 'Daily'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>fire_supervision_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>{'label':_'not_daily'}</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>{'label': 'Not daily'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>first_aid_kits_location_service_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>{'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>{'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>first_aid_kits_location_service_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>{'label':_'not_monthly'}</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>{'label': 'Not monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>first_aid_kits_location_designated_service_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>{'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>{'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>first_aid_kits_location_designated_service_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>{'label':_'not_monthly'}</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>{'label': 'Not monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>fire_extinguisher_service_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>{'label':_'daily'}</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>{'label': 'Daily'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>fire_extinguisher_service_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>{'label':_'not_daily'}</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>{'label': 'Not daily'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>emergency_exit_path_condition_service_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>{'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>{'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>emergency_exit_path_condition_service_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>{'label':_'not_monthly'}</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>{'label': 'Not monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_location_service_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>{'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>{'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_location_service_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>{'label':_'not_monthly'}</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>{'label': 'Not monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_condition_service_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>{'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>{'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_condition_service_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>{'label':_'not_monthly'}</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>{'label': 'Not monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>first_aid_kits_service_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>{'label':_'daily'}</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>{'label': 'Daily'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>first_aid_kits_service_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>{'label':_'not_daily'}</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>{'label': 'Not daily'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>emergency_exit_path_designated_service_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>{'label':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>{'label': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>emergency_exit_path_designated_service_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>{'label':_'not_monthly'}</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>{'label': 'Not monthly'}</t>
+          <t>Not visible</t>
         </is>
       </c>
     </row>
